--- a/reports/2026-03-02.xlsx
+++ b/reports/2026-03-02.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Pullback Setups" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Global Top 20'!$A$1:$N$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Global Top 20'!$A$1:$N$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Reversal Setups'!$A$1:$U$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Breakout Setups'!$A$1:$U$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Breakout Immediate 1-5D'!$A$1:$U$1</definedName>
@@ -554,7 +554,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-02 05:19 UTC</t>
+          <t>2026-03-02 20:31 UTC</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,12 +716,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HYPEUSDT</t>
+          <t>ASTERUSDT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hyperliquid</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -730,37 +730,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>55.05</v>
+        <v>84.19</v>
       </c>
       <c r="F2" t="n">
-        <v>55.05</v>
+        <v>84.19</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>$31.04</t>
+          <t>$0.68</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>$8.00B</t>
+          <t>$1.69B</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>$13.17M</t>
+          <t>$6.45M</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>348861448.9835004</v>
+        <v>149799007.0537431</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04361326759380886</v>
+        <v>0.0885538317107229</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03775324725152682</v>
+        <v>0.04308065116936798</v>
       </c>
       <c r="N2" t="inlineStr"/>
     </row>
@@ -784,37 +784,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>54.32</v>
+        <v>73.64</v>
       </c>
       <c r="F3" t="n">
-        <v>54.32</v>
+        <v>73.64</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>$1.18</t>
+          <t>$1.32</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>$1.52B</t>
+          <t>$1.70B</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>$9.50M</t>
+          <t>$21.67M</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>239643664.6736679</v>
+        <v>515619515.7980182</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1575752457475599</v>
+        <v>0.3031027359585524</v>
       </c>
       <c r="M3" t="n">
-        <v>0.039621803503255</v>
+        <v>0.04202942233026179</v>
       </c>
       <c r="N3" t="inlineStr"/>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LINKUSDT</t>
+          <t>LTCUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -838,37 +838,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>52.12</v>
+        <v>64.72</v>
       </c>
       <c r="F4" t="n">
-        <v>52.12</v>
+        <v>64.72</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>$8.79</t>
+          <t>$54.70</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>$6.21B</t>
+          <t>$4.21B</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>$17.10M</t>
+          <t>$13.14M</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>731421674.6577539</v>
+        <v>392603311.437085</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1177216351932469</v>
+        <v>0.09323265639911205</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0233832539567587</v>
+        <v>0.0334574128575708</v>
       </c>
       <c r="N4" t="inlineStr"/>
     </row>
@@ -878,12 +878,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DOTUSDT</t>
+          <t>HYPEUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Hyperliquid</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -892,37 +892,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>47.73</v>
+        <v>58.87</v>
       </c>
       <c r="F5" t="n">
-        <v>47.73</v>
+        <v>58.87</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$1.54</t>
+          <t>$32.26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>$2.58B</t>
+          <t>$8.31B</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>$7.89M</t>
+          <t>$15.24M</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>209623625.2039989</v>
+        <v>438055015.5784655</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08113879184139836</v>
+        <v>0.05269869142680897</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03763851833647941</v>
+        <v>0.03479986679268922</v>
       </c>
       <c r="N5" t="inlineStr"/>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AVAXUSDT</t>
+          <t>LINKUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -946,37 +946,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>42.84</v>
+        <v>52.12</v>
       </c>
       <c r="F6" t="n">
-        <v>42.84</v>
+        <v>52.12</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>$9.07</t>
+          <t>$9.00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>$3.92B</t>
+          <t>$6.38B</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>$14.24M</t>
+          <t>$24.33M</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>326323747.5167649</v>
+        <v>860287201.6251225</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08332770315429132</v>
+        <v>0.1348913421666246</v>
       </c>
       <c r="M6" t="n">
-        <v>0.04365103567054431</v>
+        <v>0.02828332040280982</v>
       </c>
       <c r="N6" t="inlineStr"/>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UNIUSDT</t>
+          <t>DOTUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1000,37 +1000,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>41.35</v>
+        <v>47.73</v>
       </c>
       <c r="F7" t="n">
-        <v>41.35</v>
+        <v>47.73</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>$3.81</t>
+          <t>$1.52</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>$2.41B</t>
+          <t>$2.55B</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>$6.61M</t>
+          <t>$11.70M</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>247079508.193014</v>
+        <v>270822464.2359992</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1023430964946593</v>
+        <v>0.1063241201319681</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02674469747138196</v>
+        <v>0.04321803012175747</v>
       </c>
       <c r="N7" t="inlineStr"/>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LTCUSDT</t>
+          <t>AVAXUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>34.72</v>
+        <v>42.84</v>
       </c>
       <c r="F8" t="n">
-        <v>34.72</v>
+        <v>42.84</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>$53.88</t>
+          <t>$9.21</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>$4.14B</t>
+          <t>$3.98B</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>$8.12M</t>
+          <t>$17.32M</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>300266165.9200762</v>
+        <v>394257065.8383951</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07252870243591239</v>
+        <v>0.09906622809804576</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02703190362833118</v>
+        <v>0.0439198607821468</v>
       </c>
       <c r="N8" t="inlineStr"/>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ADAUSDT</t>
+          <t>UNIUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1108,37 +1108,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>34.02</v>
+        <v>41.35</v>
       </c>
       <c r="F9" t="n">
-        <v>34.02</v>
+        <v>41.35</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>$0.28</t>
+          <t>$3.92</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>$9.92B</t>
+          <t>$2.48B</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>$15.90M</t>
+          <t>$8.29M</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>544304990.3503668</v>
+        <v>295796592.3817254</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05488220713453484</v>
+        <v>0.1190719921925795</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02921733850494961</v>
+        <v>0.0280365270378022</v>
       </c>
       <c r="N9" t="inlineStr"/>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AAVEUSDT</t>
+          <t>TAOUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1162,37 +1162,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>27.44</v>
+        <v>39.09</v>
       </c>
       <c r="F10" t="n">
-        <v>27.44</v>
+        <v>39.09</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>$115.14</t>
+          <t>$185.61</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>$1.76B</t>
+          <t>$1.99B</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>$10.20M</t>
+          <t>$5.36M</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>528839482.666045</v>
+        <v>145697212.2880533</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2996621209382478</v>
+        <v>0.07312624840376186</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01929185273491127</v>
+        <v>0.03678642896340081</v>
       </c>
       <c r="N10" t="inlineStr"/>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SUIUSDT</t>
+          <t>FILUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1216,37 +1216,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>26.19</v>
+        <v>36.51</v>
       </c>
       <c r="F11" t="n">
-        <v>26.19</v>
+        <v>36.51</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>$0.90</t>
+          <t>$0.99</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>$3.51B</t>
+          <t>$751.93M</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>$27.58M</t>
+          <t>$5.50M</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>780225268.3714583</v>
+        <v>118939676.0537201</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2225172335787013</v>
+        <v>0.1581797821533696</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0353441679831255</v>
+        <v>0.0462715852228678</v>
       </c>
       <c r="N11" t="inlineStr"/>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ZECUSDT</t>
+          <t>ENAUSDT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Zcash</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1270,37 +1270,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>23.43</v>
+        <v>32.87</v>
       </c>
       <c r="F12" t="n">
-        <v>23.43</v>
+        <v>32.87</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>$216.35</t>
+          <t>$0.12</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>$3.58B</t>
+          <t>$947.97M</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>$7.34M</t>
+          <t>$6.06M</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>278006261.8066853</v>
+        <v>148419830.6225288</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07764426307396398</v>
+        <v>0.1565652779875205</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0263971430798309</v>
+        <v>0.04084853698269705</v>
       </c>
       <c r="N12" t="inlineStr"/>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PEPEUSDT</t>
+          <t>AAVEUSDT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pepe</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1324,37 +1324,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>22.95</v>
+        <v>32.05</v>
       </c>
       <c r="F13" t="n">
-        <v>22.95</v>
+        <v>32.05</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$122.48</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>$1.42B</t>
+          <t>$1.88B</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>$12.08M</t>
+          <t>$11.78M</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>355890332.7937319</v>
+        <v>619833098.7360663</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2511026129667584</v>
+        <v>0.3298828032543321</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03393889831704171</v>
+        <v>0.01901176691601273</v>
       </c>
       <c r="N13" t="inlineStr"/>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BCHUSDT</t>
+          <t>SUIUSDT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bitcoin Cash</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1378,42 +1378,312 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>21.22</v>
+        <v>28.47</v>
       </c>
       <c r="F14" t="n">
-        <v>21.22</v>
+        <v>28.47</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>$449.70</t>
+          <t>$0.93</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>$8.99B</t>
+          <t>$3.63B</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>$6.41M</t>
+          <t>$29.44M</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>317450655.7132597</v>
+        <v>964364155.0817319</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03533039878974419</v>
+        <v>0.2653474568878068</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0201887984310511</v>
+        <v>0.03052492874976791</v>
       </c>
       <c r="N14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>APTUSDT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Aptos</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>reversal</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>28.16</v>
+      </c>
+      <c r="F15" t="n">
+        <v>28.16</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>$754.77M</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>$7.03M</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>112059274.2032642</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.1484683007607292</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.06271162625462814</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TONUSDT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Toncoin</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>reversal</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="F16" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>$1.23</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>$3.02B</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>$5.35M</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>114010417.3535755</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.03779604704448724</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.04696659177550208</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ZECUSDT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Zcash</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>reversal</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="F17" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>$219.12</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>$3.63B</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>$7.51M</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>284554206.4542146</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.07834417374767171</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.02637879669231937</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PEPEUSDT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Pepe</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>reversal</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="F18" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>$1.48B</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>$15.14M</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>438578012.0813236</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.296950855751128</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.03451941176126903</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BCHUSDT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bitcoin Cash</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>reversal</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="F19" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>$442.20</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>$8.86B</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>$8.13M</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>406565779.1607104</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.04590628232985167</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.02000330135209255</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N14"/>
+  <autoFilter ref="A1:N19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1563,17 +1833,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HYPEUSDT</t>
+          <t>ASTERUSDT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hyperliquid</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$31.04</t>
+          <t>$0.68</t>
         </is>
       </c>
       <c r="E2" t="b">
@@ -1581,37 +1851,37 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>$8.00B</t>
+          <t>$1.69B</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>$13.17M</t>
+          <t>$6.45M</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>348861448.9835004</v>
+        <v>149799007.0537431</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04361326759380886</v>
+        <v>0.0885538317107229</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03775324725152682</v>
+        <v>0.04308065116936798</v>
       </c>
       <c r="P2" t="n">
-        <v>55.05</v>
+        <v>84.19</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>80.45</v>
+        <v>95.34</v>
       </c>
       <c r="S2" t="n">
-        <v>77.29000000000001</v>
+        <v>63.97</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U2" t="inlineStr"/>
     </row>
@@ -1631,7 +1901,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$1.18</t>
+          <t>$1.32</t>
         </is>
       </c>
       <c r="E3" t="b">
@@ -1639,25 +1909,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>$1.52B</t>
+          <t>$1.70B</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>$9.50M</t>
+          <t>$21.67M</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>239643664.6736679</v>
+        <v>515619515.7980182</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1575752457475599</v>
+        <v>0.3031027359585524</v>
       </c>
       <c r="O3" t="n">
-        <v>0.039621803503255</v>
+        <v>0.04202942233026179</v>
       </c>
       <c r="P3" t="n">
-        <v>54.32</v>
+        <v>73.64</v>
       </c>
       <c r="Q3" t="n">
         <v>100</v>
@@ -1669,7 +1939,7 @@
         <v>70</v>
       </c>
       <c r="T3" t="n">
-        <v>9.02</v>
+        <v>73.42</v>
       </c>
       <c r="U3" t="inlineStr"/>
     </row>
@@ -1679,17 +1949,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LINKUSDT</t>
+          <t>LTCUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$8.79</t>
+          <t>$54.70</t>
         </is>
       </c>
       <c r="E4" t="b">
@@ -1697,37 +1967,37 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>$6.21B</t>
+          <t>$4.21B</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>$17.10M</t>
+          <t>$13.14M</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>731421674.6577539</v>
+        <v>392603311.437085</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1177216351932469</v>
+        <v>0.09323265639911205</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0233832539567587</v>
+        <v>0.0334574128575708</v>
       </c>
       <c r="P4" t="n">
-        <v>52.12</v>
+        <v>64.72</v>
       </c>
       <c r="Q4" t="n">
         <v>100</v>
       </c>
       <c r="R4" t="n">
-        <v>86.95999999999999</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
       </c>
       <c r="T4" t="n">
-        <v>60.1</v>
+        <v>100</v>
       </c>
       <c r="U4" t="inlineStr"/>
     </row>
@@ -1737,17 +2007,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DOTUSDT</t>
+          <t>HYPEUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Hyperliquid</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$1.54</t>
+          <t>$32.26</t>
         </is>
       </c>
       <c r="E5" t="b">
@@ -1755,37 +2025,37 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>$2.58B</t>
+          <t>$8.31B</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>$7.89M</t>
+          <t>$15.24M</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>209623625.2039989</v>
+        <v>438055015.5784655</v>
       </c>
       <c r="N5" t="n">
-        <v>0.08113879184139836</v>
+        <v>0.05269869142680897</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03763851833647941</v>
+        <v>0.03479986679268922</v>
       </c>
       <c r="P5" t="n">
-        <v>47.73</v>
+        <v>58.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>65.78</v>
+        <v>80.45</v>
       </c>
       <c r="S5" t="n">
-        <v>70</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>12.74</v>
       </c>
       <c r="U5" t="inlineStr"/>
     </row>
@@ -1795,17 +2065,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AVAXUSDT</t>
+          <t>LINKUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>$9.07</t>
+          <t>$9.00</t>
         </is>
       </c>
       <c r="E6" t="b">
@@ -1813,37 +2083,37 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>$3.92B</t>
+          <t>$6.38B</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>$14.24M</t>
+          <t>$24.33M</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>326323747.5167649</v>
+        <v>860287201.6251225</v>
       </c>
       <c r="N6" t="n">
-        <v>0.08332770315429132</v>
+        <v>0.1348913421666246</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04365103567054431</v>
+        <v>0.02828332040280982</v>
       </c>
       <c r="P6" t="n">
-        <v>42.84</v>
+        <v>52.12</v>
       </c>
       <c r="Q6" t="n">
         <v>100</v>
       </c>
       <c r="R6" t="n">
-        <v>85.14</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>23.4</v>
+        <v>20</v>
       </c>
       <c r="T6" t="n">
-        <v>26.47</v>
+        <v>60.1</v>
       </c>
       <c r="U6" t="inlineStr"/>
     </row>
@@ -1853,17 +2123,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UNIUSDT</t>
+          <t>DOTUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$3.81</t>
+          <t>$1.52</t>
         </is>
       </c>
       <c r="E7" t="b">
@@ -1871,34 +2141,34 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>$2.41B</t>
+          <t>$2.55B</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>$6.61M</t>
+          <t>$11.70M</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>247079508.193014</v>
+        <v>270822464.2359992</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1023430964946593</v>
+        <v>0.1063241201319681</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02674469747138196</v>
+        <v>0.04321803012175747</v>
       </c>
       <c r="P7" t="n">
-        <v>41.35</v>
+        <v>47.73</v>
       </c>
       <c r="Q7" t="n">
         <v>100</v>
       </c>
       <c r="R7" t="n">
-        <v>78.42</v>
+        <v>65.78</v>
       </c>
       <c r="S7" t="n">
-        <v>44.55</v>
+        <v>70</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1911,17 +2181,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LTCUSDT</t>
+          <t>AVAXUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$53.88</t>
+          <t>$9.21</t>
         </is>
       </c>
       <c r="E8" t="b">
@@ -1929,37 +2199,37 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>$4.14B</t>
+          <t>$3.98B</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>$8.12M</t>
+          <t>$17.32M</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>300266165.9200762</v>
+        <v>394257065.8383951</v>
       </c>
       <c r="N8" t="n">
-        <v>0.07252870243591239</v>
+        <v>0.09906622809804576</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02703190362833118</v>
+        <v>0.0439198607821468</v>
       </c>
       <c r="P8" t="n">
-        <v>34.72</v>
+        <v>42.84</v>
       </c>
       <c r="Q8" t="n">
         <v>100</v>
       </c>
       <c r="R8" t="n">
-        <v>89.06999999999999</v>
+        <v>85.14</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>23.4</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>26.47</v>
       </c>
       <c r="U8" t="inlineStr"/>
     </row>
@@ -1969,17 +2239,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ADAUSDT</t>
+          <t>UNIUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$0.28</t>
+          <t>$3.92</t>
         </is>
       </c>
       <c r="E9" t="b">
@@ -1987,34 +2257,34 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>$9.92B</t>
+          <t>$2.48B</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>$15.90M</t>
+          <t>$8.29M</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>544304990.3503668</v>
+        <v>295796592.3817254</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05488220713453484</v>
+        <v>0.1190719921925795</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02921733850494961</v>
+        <v>0.0280365270378022</v>
       </c>
       <c r="P9" t="n">
-        <v>34.02</v>
+        <v>41.35</v>
       </c>
       <c r="Q9" t="n">
         <v>100</v>
       </c>
       <c r="R9" t="n">
-        <v>85.06999999999999</v>
+        <v>78.42</v>
       </c>
       <c r="S9" t="n">
-        <v>21.25</v>
+        <v>44.55</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -2027,17 +2297,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AAVEUSDT</t>
+          <t>TAOUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$115.14</t>
+          <t>$185.61</t>
         </is>
       </c>
       <c r="E10" t="b">
@@ -2045,37 +2315,37 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>$1.76B</t>
+          <t>$1.99B</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>$10.20M</t>
+          <t>$5.36M</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>528839482.666045</v>
+        <v>145697212.2880533</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2996621209382478</v>
+        <v>0.07312624840376186</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01929185273491127</v>
+        <v>0.03678642896340081</v>
       </c>
       <c r="P10" t="n">
-        <v>27.44</v>
+        <v>39.09</v>
       </c>
       <c r="Q10" t="n">
         <v>100</v>
       </c>
       <c r="R10" t="n">
-        <v>91.47</v>
+        <v>89.53</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>34.99</v>
       </c>
       <c r="U10" t="inlineStr"/>
     </row>
@@ -2085,17 +2355,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SUIUSDT</t>
+          <t>FILUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>$0.90</t>
+          <t>$0.99</t>
         </is>
       </c>
       <c r="E11" t="b">
@@ -2103,37 +2373,37 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>$3.51B</t>
+          <t>$751.93M</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>$27.58M</t>
+          <t>$5.50M</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>780225268.3714583</v>
+        <v>118939676.0537201</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2225172335787013</v>
+        <v>0.1581797821533696</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0353441679831255</v>
+        <v>0.0462715852228678</v>
       </c>
       <c r="P11" t="n">
-        <v>26.19</v>
+        <v>36.51</v>
       </c>
       <c r="Q11" t="n">
         <v>100</v>
       </c>
       <c r="R11" t="n">
-        <v>87.31</v>
+        <v>79.16</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>27.51</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="U11" t="inlineStr"/>
     </row>
@@ -2733,7 +3003,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$31.04</t>
+          <t>$32.26</t>
         </is>
       </c>
       <c r="E2" t="b">
@@ -2741,25 +3011,25 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>$8.00B</t>
+          <t>$8.31B</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>$13.17M</t>
+          <t>$15.24M</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>348861448.9835004</v>
+        <v>438055015.5784655</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04361326759380886</v>
+        <v>0.05269869142680897</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03775324725152682</v>
+        <v>0.03479986679268922</v>
       </c>
       <c r="P2" t="n">
-        <v>40.26</v>
+        <v>43.46</v>
       </c>
       <c r="Q2" t="n">
         <v>40</v>
@@ -2768,10 +3038,10 @@
         <v>20</v>
       </c>
       <c r="S2" t="n">
-        <v>81.29000000000001</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>7.36</v>
+        <v>39.1</v>
       </c>
       <c r="U2" t="inlineStr"/>
     </row>
@@ -2781,17 +3051,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UNIUSDT</t>
+          <t>ASTERUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$3.81</t>
+          <t>$0.68</t>
         </is>
       </c>
       <c r="E3" t="b">
@@ -2799,43 +3069,39 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>$2.41B</t>
+          <t>$1.69B</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>$6.61M</t>
+          <t>$6.45M</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>247079508.193014</v>
+        <v>149799007.0537431</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1023430964946593</v>
+        <v>0.0885538317107229</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02674469747138196</v>
+        <v>0.04308065116936798</v>
       </c>
       <c r="P3" t="n">
-        <v>22.26</v>
+        <v>42.39</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R3" t="n">
+        <v>80</v>
+      </c>
+      <c r="S3" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="T3" t="n">
         <v>100</v>
       </c>
-      <c r="S3" t="n">
-        <v>22.55</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>broken_trend</t>
-        </is>
-      </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2843,17 +3109,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AVAXUSDT</t>
+          <t>UNIUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$9.07</t>
+          <t>$3.92</t>
         </is>
       </c>
       <c r="E4" t="b">
@@ -2861,25 +3127,25 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>$3.92B</t>
+          <t>$2.48B</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>$14.24M</t>
+          <t>$8.29M</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>326323747.5167649</v>
+        <v>295796592.3817254</v>
       </c>
       <c r="N4" t="n">
-        <v>0.08332770315429132</v>
+        <v>0.1190719921925795</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04365103567054431</v>
+        <v>0.0280365270378022</v>
       </c>
       <c r="P4" t="n">
-        <v>20.34</v>
+        <v>23.86</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -2888,10 +3154,10 @@
         <v>100</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4</v>
+        <v>38.55</v>
       </c>
       <c r="T4" t="n">
-        <v>59.71</v>
+        <v>0</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -2905,17 +3171,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DOTUSDT</t>
+          <t>AVAXUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$1.54</t>
+          <t>$9.21</t>
         </is>
       </c>
       <c r="E5" t="b">
@@ -2923,37 +3189,37 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>$2.58B</t>
+          <t>$3.98B</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>$7.89M</t>
+          <t>$17.32M</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>209623625.2039989</v>
+        <v>394257065.8383951</v>
       </c>
       <c r="N5" t="n">
-        <v>0.08113879184139836</v>
+        <v>0.09906622809804576</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03763851833647941</v>
+        <v>0.0439198607821468</v>
       </c>
       <c r="P5" t="n">
-        <v>10.8</v>
+        <v>22.74</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="S5" t="n">
-        <v>28</v>
+        <v>27.4</v>
       </c>
       <c r="T5" t="n">
-        <v>6.81</v>
+        <v>59.71</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -2967,17 +3233,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NEARUSDT</t>
+          <t>DOTUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>$1.18</t>
+          <t>$1.52</t>
         </is>
       </c>
       <c r="E6" t="b">
@@ -2985,37 +3251,37 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>$1.52B</t>
+          <t>$2.55B</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>$9.50M</t>
+          <t>$11.70M</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>239643664.6736679</v>
+        <v>270822464.2359992</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1575752457475599</v>
+        <v>0.1063241201319681</v>
       </c>
       <c r="O6" t="n">
-        <v>0.039621803503255</v>
+        <v>0.04321803012175747</v>
       </c>
       <c r="P6" t="n">
-        <v>7.2</v>
+        <v>10.8</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="S6" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="T6" t="n">
-        <v>33.54</v>
+        <v>6.81</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -3029,17 +3295,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AAVEUSDT</t>
+          <t>NEARUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$115.14</t>
+          <t>$1.32</t>
         </is>
       </c>
       <c r="E7" t="b">
@@ -3047,25 +3313,25 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>$1.76B</t>
+          <t>$1.70B</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>$10.20M</t>
+          <t>$21.67M</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>528839482.666045</v>
+        <v>515619515.7980182</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2996621209382478</v>
+        <v>0.3031027359585524</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01929185273491127</v>
+        <v>0.04202942233026179</v>
       </c>
       <c r="P7" t="n">
-        <v>2.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -3074,10 +3340,10 @@
         <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -3091,17 +3357,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BCHUSDT</t>
+          <t>APTUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bitcoin Cash</t>
+          <t>Aptos</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$449.70</t>
+          <t>$0.97</t>
         </is>
       </c>
       <c r="E8" t="b">
@@ -3109,25 +3375,25 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>$8.99B</t>
+          <t>$754.77M</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>$6.41M</t>
+          <t>$7.03M</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>317450655.7132597</v>
+        <v>112059274.2032642</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03533039878974419</v>
+        <v>0.1484683007607292</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0201887984310511</v>
+        <v>0.06271162625462814</v>
       </c>
       <c r="P8" t="n">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -3136,10 +3402,10 @@
         <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -3153,17 +3419,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ADAUSDT</t>
+          <t>ENAUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$0.28</t>
+          <t>$0.12</t>
         </is>
       </c>
       <c r="E9" t="b">
@@ -3171,25 +3437,25 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>$9.92B</t>
+          <t>$947.97M</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>$15.90M</t>
+          <t>$6.06M</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>544304990.3503668</v>
+        <v>148419830.6225288</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05488220713453484</v>
+        <v>0.1565652779875205</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02921733850494961</v>
+        <v>0.04084853698269705</v>
       </c>
       <c r="P9" t="n">
-        <v>2.13</v>
+        <v>6.72</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -3198,10 +3464,10 @@
         <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>1.25</v>
+        <v>47.18</v>
       </c>
       <c r="T9" t="n">
-        <v>0.72</v>
+        <v>100</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -3215,17 +3481,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SUIUSDT</t>
+          <t>TAOUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$0.90</t>
+          <t>$185.61</t>
         </is>
       </c>
       <c r="E10" t="b">
@@ -3233,25 +3499,25 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>$3.51B</t>
+          <t>$1.99B</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>$27.58M</t>
+          <t>$5.36M</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>780225268.3714583</v>
+        <v>145697212.2880533</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2225172335787013</v>
+        <v>0.07312624840376186</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0353441679831255</v>
+        <v>0.03678642896340081</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>6.43</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -3260,10 +3526,10 @@
         <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>44.34</v>
       </c>
       <c r="T10" t="n">
-        <v>18.34</v>
+        <v>80</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -3277,17 +3543,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LINKUSDT</t>
+          <t>SUIUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>$8.79</t>
+          <t>$0.93</t>
         </is>
       </c>
       <c r="E11" t="b">
@@ -3295,25 +3561,25 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>$6.21B</t>
+          <t>$3.63B</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>$17.10M</t>
+          <t>$29.44M</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>731421674.6577539</v>
+        <v>964364155.0817319</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1177216351932469</v>
+        <v>0.2653474568878068</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0233832539567587</v>
+        <v>0.03052492874976791</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -3322,10 +3588,10 @@
         <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>31.38</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
